--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2025.xlsx
@@ -592,27 +592,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff6a7e61eb5+80197]
+	GetHandleVerifier [0x0x7ff6a7e61f10+80288]
+	(No symbol) [0x0x7ff6a7be02fa]
+	(No symbol) [0x0x7ff6a7c37cd7]
+	(No symbol) [0x0x7ff6a7c37f9c]
+	(No symbol) [0x0x7ff6a7c8ba87]
+	(No symbol) [0x0x7ff6a7c603bf]
+	(No symbol) [0x0x7ff6a7c887fb]
+	(No symbol) [0x0x7ff6a7c60153]
+	(No symbol) [0x0x7ff6a7c28b02]
+	(No symbol) [0x0x7ff6a7c298d3]
+	GetHandleVerifier [0x0x7ff6a811e83d+2949837]
+	GetHandleVerifier [0x0x7ff6a8118c6a+2926330]
+	GetHandleVerifier [0x0x7ff6a81386c7+3055959]
+	GetHandleVerifier [0x0x7ff6a7e7cfee+191102]
+	GetHandleVerifier [0x0x7ff6a7e850af+224063]
+	GetHandleVerifier [0x0x7ff6a7e6af64+117236]
+	GetHandleVerifier [0x0x7ff6a7e6b119+117673]
+	GetHandleVerifier [0x0x7ff6a7e510a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -714,27 +714,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff6bc3c1eb5+80197]
+	GetHandleVerifier [0x0x7ff6bc3c1f10+80288]
+	(No symbol) [0x0x7ff6bc1402fa]
+	(No symbol) [0x0x7ff6bc197cd7]
+	(No symbol) [0x0x7ff6bc197f9c]
+	(No symbol) [0x0x7ff6bc1eba87]
+	(No symbol) [0x0x7ff6bc1c03bf]
+	(No symbol) [0x0x7ff6bc1e87fb]
+	(No symbol) [0x0x7ff6bc1c0153]
+	(No symbol) [0x0x7ff6bc188b02]
+	(No symbol) [0x0x7ff6bc1898d3]
+	GetHandleVerifier [0x0x7ff6bc67e83d+2949837]
+	GetHandleVerifier [0x0x7ff6bc678c6a+2926330]
+	GetHandleVerifier [0x0x7ff6bc6986c7+3055959]
+	GetHandleVerifier [0x0x7ff6bc3dcfee+191102]
+	GetHandleVerifier [0x0x7ff6bc3e50af+224063]
+	GetHandleVerifier [0x0x7ff6bc3caf64+117236]
+	GetHandleVerifier [0x0x7ff6bc3cb119+117673]
+	GetHandleVerifier [0x0x7ff6bc3b10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -783,17 +783,17 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.30</t>
+                  £15.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.30</t>
+          <t>£15.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.30</t>
+          <t>£15.25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -836,27 +836,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.45</t>
+                  £15.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.45</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.45</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -958,27 +958,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1080,27 +1080,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1202,27 +1202,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.95</t>
+                  £21.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,27 +1324,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1393,17 +1393,17 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £25.18</t>
+                  £25.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.18</t>
+          <t>£25.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.18</t>
+          <t>£25.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,27 +1446,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1515,17 +1515,17 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £27.27</t>
+                  £27.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.27</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.27</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1568,27 +1568,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.82</t>
+                  £26.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,27 +1690,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1809,1705 +1809,1710 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 300.000
+  (Session info: chrome=140.0.7339.208)
+Stacktrace:
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b74d78d]
+	(No symbol) [0x0x7ff66b74d47b]
+	(No symbol) [0x0x7ff66b74afec]
+	(No symbol) [0x0x7ff66b74ba6b]
+	(No symbol) [0x0x7ff66b75aa7e]
+	(No symbol) [0x0x7ff66b770e31]
+	(No symbol) [0x0x7ff66b7780da]
+	(No symbol) [0x0x7ff66b74c21e]
+	(No symbol) [0x0x7ff66b770b66]
+	(No symbol) [0x0x7ff66b8086d2]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>£32.97</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>£50.96</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>£36.30 Pre Sale Price-£39.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>120mm Celotex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>120mm Celotex XR4120 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £32.89</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£32.89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£32.89</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£34.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£34.10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£33.70</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£32.92</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£33.72</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>£32.72</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>£32.97</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>£50.96</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>£34.0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>£66.89</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>£51.70</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>£36.30 Pre Sale Price-£39.99</t>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>£34.90 Pre Sale Price-£37.99</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>120mm Celotex</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>120mm Celotex XR4120 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>130mm Celotex</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130mm Celotex XR4130 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.92</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£32.92</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£32.92</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£34.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£34.10</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£33.70</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£32.92</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>£35.08</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>£33.72</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>£32.72</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+                  £40.15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>£40.15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>£40.15</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>£40.27</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>£40.25</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>£40.18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>£46.74</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/130mm-celotex-xr4130-pir-insulation-board-2400mm-x-1200mm-x-130mm</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>£39.88</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>£34.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>£66.89</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>£51.70</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>£38.6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>£73.80</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>£61.93</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>£34.90 Pre Sale Price-£37.99</t>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>£717.24</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>£41.09 Pre Sale Price-£44.99</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>130mm Celotex</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130mm Celotex XR4130 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Regular price
-                  £40.18</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>£40.18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>£40.18</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>£41.00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>£40.27</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>£40.25</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>£40.18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>£46.74</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>£41.10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>£39.88</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>140mm Celotex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>140mm Celotex XR4140 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£40.95</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>£40.95</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>£41.06</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£41.05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>£40.95</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£41.93</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>£38.70</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>£38.6</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>£73.80</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>£61.93</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>£43.83</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>£78.85</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>£65.16</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>£717.24</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>£41.09 Pre Sale Price-£44.99</t>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>£717.6</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>140mm Celotex</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>140mm Celotex XR4140 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150mm Celotex</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150mm Celotex XR4150 2.4m X 1.2m</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £40.85</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£40.85</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£40.85</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>£40.96</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>£40.95</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>£41.06</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>£41.05</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>£41.00</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>£41.93</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>£38.70</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>£40.89</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>£43.58</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£41.86</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>£39.50</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>£43.83</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>£78.85</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>£65.16</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>£42.21</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>£82.06</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>£74.88</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>£717.6</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>N/L</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>£43.50 Pre Sale Price-£49.99</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>150mm Celotex</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150mm Celotex XR4150 2.4m X 1.2m</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>165mm Celotex1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>165mm Celotex XR4165 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.89</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>£40.89</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£40.89</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>£41.50</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>£40.96</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>£40.95</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>£40.89</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>£43.58</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>£41.86</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>£39.50</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+                  £695.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>£877.92</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>£719.88</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>£768.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>£857.88</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>£695.52</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>£653.19</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>£959.7</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>xr4200pal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200mm Celotex XR4200 2.4m x 1.2m </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £895.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>£960.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>£935.88</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>£984.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>£1029.48</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>£1407.24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>£873.16</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>£42.21</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>£82.06</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>£74.88</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>£43.50 Pre Sale Price-£49.99</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>£861.09</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>£1164.06</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>£1073.28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>£962.37 Pre Sale Price-£1,040.00</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>165mm Celotex1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>165mm Celotex XR4165 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Regular price
-                  £695.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>£695.00</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>£695.00</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>£695.00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>£877.92</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>£719.88</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>£768.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>£857.88</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>£695.52</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>£653.19</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>£959.7</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>xr4200pal</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200mm Celotex XR4200 2.4m x 1.2m </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Regular price
-                  £895.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>£895.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>£895.00</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>£895.00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>£960.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>£935.88</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>£984.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>£1029.48</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>£1407.24</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>£873.16</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PL4025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Celotex PL4025 37.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>£29.45</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>£35.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>£29.80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>£29.58</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>£29.82</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>£28.41</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>£861.09</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>£1164.06</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>£1073.28</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>£962.37 Pre Sale Price-£1,040.00</t>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>£36.95</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>£68.31</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>£48.24</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>£49.22</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>£37.58</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PL4025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Celotex PL4025 37.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£29.45</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>£29.45</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>£29.45</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>£35.00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>£29.80</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>£37.39</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>£29.82</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>£28.41</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PL4040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Celotex PL4040 52.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£43.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>£36.74</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>£34.30</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>£36.95</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>£68.31</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>£48.24</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>£49.22</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>£37.58</t>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>£44.24</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>£79.12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>£58.53</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>£49.55</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>£45.67</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PL4040</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Celotex PL4040 52.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>£43.00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>£36.74</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>£34.30</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PL4050</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Celotex PL4050 62.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£39.10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>£39.10</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>£39.10</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>£47.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>£40.21</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£49.49</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>£40.21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>£37.24</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>£44.24</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>£79.12</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>£58.53</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>£49.55</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>£45.67</t>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>£52.32</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>£87.37</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>£66.08</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>£68.97</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>£50.69</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PL4050</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Celotex PL4050 62.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£39.10</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>£39.10</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>£39.10</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>£47.00</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>£39.15</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>£39.15</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>£40.21</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>£49.49</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>£40.21</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>£37.24</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PL4060</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Celotex PL4060 72.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£43.59</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>£43.59</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>£43.59</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>£54.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>£46.88</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>£54.99</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>£44.52</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>£42.45</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>£52.32</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>£87.37</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>£66.08</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>£68.97</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>£50.69</t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>£55.49</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>£92.82</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>£68.87</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>£79.88</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>£55.30</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PL4060</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Celotex PL4060 72.5mm x 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£43.59</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>£43.59</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>£43.59</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>£54.00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>£43.62</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>£43.62</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>£46.88</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>£54.99</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>£44.52</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>£42.45</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>celcav50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 50mm </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>£49.60</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>£78.54</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>£43.55</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>£55.49</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>£92.82</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>£68.87</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>£79.88</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>£55.30</t>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>£41.25</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>£68.43</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>£65.48</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>£60.57</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>£44.23</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>celcav50</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 50mm </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£43.80</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>£43.80</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>£43.80</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>£45.00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>£49.60</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>£43.99</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>£43.80</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>£78.54</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>£43.55</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cw40755</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 75mm </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£43.85</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>£43.85</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>£43.85</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>£48.04</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>£43.90</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>£43.30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>£85.44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>£47.03</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>£41.25</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>£68.43</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>£65.48</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>£39.38</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>£71.62</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>£63.59</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>£60.57</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>£44.23</t>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>£68.48</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>£49.06</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cw40755</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 75mm </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£43.85</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>£43.85</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>£43.85</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>£44.00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>£48.04</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>£43.90</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>£43.30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>£85.44</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>£47.03</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>celcav85</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Celotex CW 85mm (16 Packs)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>£925.00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>£992.06</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>£39.38</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>£71.62</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>£63.59</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>£68.48</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>£49.06</t>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>£1439.04</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>£1787.2</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>N/L</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>celcav85</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Celotex CW 85mm (16 Packs)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>£925.00</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>£992.06</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cw4100</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 100mm </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£42.95</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>£42.95</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>£42.95</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£46.50</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>£42.95</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>£81.9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>£43.14</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
-</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>£1439.04</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>£1787.2</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cw4100</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Celotex CW 100mm </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£43.75</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>£43.75</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>£43.75</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>£45.00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>£46.50</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>£43.99</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>£43.14</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>£81.9</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>£43.14</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
+	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
+	(No symbol) [0x0x7ff66b7602fa]
+	(No symbol) [0x0x7ff66b7b7cd7]
+	(No symbol) [0x0x7ff66b7b7f9c]
+	(No symbol) [0x0x7ff66b80ba87]
+	(No symbol) [0x0x7ff66b7e03bf]
+	(No symbol) [0x0x7ff66b8087fb]
+	(No symbol) [0x0x7ff66b7e0153]
+	(No symbol) [0x0x7ff66b7a8b02]
+	(No symbol) [0x0x7ff66b7a98d3]
+	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
+	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
+	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
+	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
+	GetHandleVerifier [0x0x7ff66ba050af+224063]
+	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
+	GetHandleVerifier [0x0x7ff66b9eb119+117673]
+	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6a7e61eb5+80197]
-	GetHandleVerifier [0x0x7ff6a7e61f10+80288]
-	(No symbol) [0x0x7ff6a7be02fa]
-	(No symbol) [0x0x7ff6a7c37cd7]
-	(No symbol) [0x0x7ff6a7c37f9c]
-	(No symbol) [0x0x7ff6a7c8ba87]
-	(No symbol) [0x0x7ff6a7c603bf]
-	(No symbol) [0x0x7ff6a7c887fb]
-	(No symbol) [0x0x7ff6a7c60153]
-	(No symbol) [0x0x7ff6a7c28b02]
-	(No symbol) [0x0x7ff6a7c298d3]
-	GetHandleVerifier [0x0x7ff6a811e83d+2949837]
-	GetHandleVerifier [0x0x7ff6a8118c6a+2926330]
-	GetHandleVerifier [0x0x7ff6a81386c7+3055959]
-	GetHandleVerifier [0x0x7ff6a7e7cfee+191102]
-	GetHandleVerifier [0x0x7ff6a7e850af+224063]
-	GetHandleVerifier [0x0x7ff6a7e6af64+117236]
-	GetHandleVerifier [0x0x7ff6a7e6b119+117673]
-	GetHandleVerifier [0x0x7ff6a7e510a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6bc3c1eb5+80197]
-	GetHandleVerifier [0x0x7ff6bc3c1f10+80288]
-	(No symbol) [0x0x7ff6bc1402fa]
-	(No symbol) [0x0x7ff6bc197cd7]
-	(No symbol) [0x0x7ff6bc197f9c]
-	(No symbol) [0x0x7ff6bc1eba87]
-	(No symbol) [0x0x7ff6bc1c03bf]
-	(No symbol) [0x0x7ff6bc1e87fb]
-	(No symbol) [0x0x7ff6bc1c0153]
-	(No symbol) [0x0x7ff6bc188b02]
-	(No symbol) [0x0x7ff6bc1898d3]
-	GetHandleVerifier [0x0x7ff6bc67e83d+2949837]
-	GetHandleVerifier [0x0x7ff6bc678c6a+2926330]
-	GetHandleVerifier [0x0x7ff6bc6986c7+3055959]
-	GetHandleVerifier [0x0x7ff6bc3dcfee+191102]
-	GetHandleVerifier [0x0x7ff6bc3e50af+224063]
-	GetHandleVerifier [0x0x7ff6bc3caf64+117236]
-	GetHandleVerifier [0x0x7ff6bc3cb119+117673]
-	GetHandleVerifier [0x0x7ff6bc3b10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -935,7 +935,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.59</t>
+          <t>£15.44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£19.85</t>
+          <t>£19.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£25.18</t>
+          <t>£24.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£27.27</t>
+          <t>£26.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.55</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.56</t>
+          <t>£35.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1809,33 +1809,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 300.000
-  (Session info: chrome=140.0.7339.208)
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b74d78d]
-	(No symbol) [0x0x7ff66b74d47b]
-	(No symbol) [0x0x7ff66b74afec]
-	(No symbol) [0x0x7ff66b74ba6b]
-	(No symbol) [0x0x7ff66b75aa7e]
-	(No symbol) [0x0x7ff66b770e31]
-	(No symbol) [0x0x7ff66b7780da]
-	(No symbol) [0x0x7ff66b74c21e]
-	(No symbol) [0x0x7ff66b770b66]
-	(No symbol) [0x0x7ff66b8086d2]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1916,7 +1911,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£32.92</t>
+          <t>£32.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1939,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2038,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£40.18</t>
+          <t>£39.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2048,7 +2043,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/130mm-celotex-xr4130-pir-insulation-board-2400mm-x-1200mm-x-130mm</t>
+          <t>£41.10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2061,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2159,7 +2154,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.54</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2182,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2281,7 +2276,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£40.89</t>
+          <t>£40.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2304,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2524,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2645,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2766,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2887,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3008,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3129,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3250,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3371,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3492,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff66b9e1eb5+80197]
-	GetHandleVerifier [0x0x7ff66b9e1f10+80288]
-	(No symbol) [0x0x7ff66b7602fa]
-	(No symbol) [0x0x7ff66b7b7cd7]
-	(No symbol) [0x0x7ff66b7b7f9c]
-	(No symbol) [0x0x7ff66b80ba87]
-	(No symbol) [0x0x7ff66b7e03bf]
-	(No symbol) [0x0x7ff66b8087fb]
-	(No symbol) [0x0x7ff66b7e0153]
-	(No symbol) [0x0x7ff66b7a8b02]
-	(No symbol) [0x0x7ff66b7a98d3]
-	GetHandleVerifier [0x0x7ff66bc9e83d+2949837]
-	GetHandleVerifier [0x0x7ff66bc98c6a+2926330]
-	GetHandleVerifier [0x0x7ff66bcb86c7+3055959]
-	GetHandleVerifier [0x0x7ff66b9fcfee+191102]
-	GetHandleVerifier [0x0x7ff66ba050af+224063]
-	GetHandleVerifier [0x0x7ff66b9eaf64+117236]
-	GetHandleVerifier [0x0x7ff66b9eb119+117673]
-	GetHandleVerifier [0x0x7ff66b9d10a8+11064]
+	GetHandleVerifier [0x0x7ff780b11eb5+80197]
+	GetHandleVerifier [0x0x7ff780b11f10+80288]
+	(No symbol) [0x0x7ff7808902fa]
+	(No symbol) [0x0x7ff7808e7cd7]
+	(No symbol) [0x0x7ff7808e7f9c]
+	(No symbol) [0x0x7ff78093ba87]
+	(No symbol) [0x0x7ff7809103bf]
+	(No symbol) [0x0x7ff7809387fb]
+	(No symbol) [0x0x7ff780910153]
+	(No symbol) [0x0x7ff7808d8b02]
+	(No symbol) [0x0x7ff7808d98d3]
+	GetHandleVerifier [0x0x7ff780dce83d+2949837]
+	GetHandleVerifier [0x0x7ff780dc8c6a+2926330]
+	GetHandleVerifier [0x0x7ff780de86c7+3055959]
+	GetHandleVerifier [0x0x7ff780b2cfee+191102]
+	GetHandleVerifier [0x0x7ff780b350af+224063]
+	GetHandleVerifier [0x0x7ff780b1af64+117236]
+	GetHandleVerifier [0x0x7ff780b1b119+117673]
+	GetHandleVerifier [0x0x7ff780b010a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
